--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试/集群管理故障测试设计_review.xlsx
@@ -887,18 +887,46 @@
         </r>
       </text>
     </comment>
-    <comment ref="A155" authorId="0">
+    <comment ref="A151" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1</t>
+        </r>
+        <r>
+          <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>Author:</t>
+          <t>、</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>attach/detach</t>
         </r>
         <r>
           <rPr>
@@ -908,8 +936,112 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
+          <t>节点流程与</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>remove/create</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">节点流程类似，此处不作设计
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">、启停节点不通知编目，因此启停节点不作编目相关的设计
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>3</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>、</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>coord</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>的重启场景类似，仅选取几个写用例，字体变灰的表示不写用例</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A165" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
           <t xml:space="preserve">
-需要考虑编目、协调、数据节点主机异常重启（目标主机）</t>
+1、节点运行时coord、data主机重启在基本操作中已有覆盖
+2、主机正常/异常重启的设计只做简单覆盖，不像节点正常/异常重启那么详细</t>
         </r>
       </text>
     </comment>
@@ -918,7 +1050,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="219">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1801,10 +1933,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在其他特性有覆盖，不考虑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>节点异常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1838,30 +1966,6 @@
   </si>
   <si>
     <t>主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord节点所在主机正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点运行过程中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG主节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点异常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2101,6 +2205,132 @@
   </si>
   <si>
     <t>操作失败；故障恢复后可以继续创建/删除节点组和节点，节点可以正常使用；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除节点组和节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataRG时连接的coord正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord正常重启</t>
+  </si>
+  <si>
+    <t>coord正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cata主节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataRG时cata主节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataRG时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除dataRG时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除dataRG时cata主节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启停节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动data节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动data节点时连接的coord正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止data节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord异常重启</t>
+  </si>
+  <si>
+    <t>cata主节点异常重启</t>
+  </si>
+  <si>
+    <t>创建dataRG时cata主节点异常重启</t>
+  </si>
+  <si>
+    <t>删除dataRG时cata主节点异常重启</t>
+  </si>
+  <si>
+    <t>节点运行过程中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除节点组和节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点所在主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataRG时目标节点所在主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataRG时cata主节点所在主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cataRG时目标节点所在主机异常重启</t>
+  </si>
+  <si>
+    <t>创建dataRG时cata主节点所在主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除dataRG时连接的coord正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止data节点时连接的coord正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动data节点时连接的coord异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除dataRG时连接的coord异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataRG时连接的coord异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期结果：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止data节点时连接的coord异常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2300,7 +2530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2350,6 +2580,12 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2359,10 +2595,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2372,6 +2614,72 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
     <mruColors>
       <color rgb="FF008A3E"/>
     </mruColors>
@@ -2387,7 +2695,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2664,17 +2972,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
     <col min="2" max="2" width="6.25" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="10" customWidth="1"/>
     <col min="4" max="4" width="14.625" style="6" customWidth="1"/>
     <col min="5" max="5" width="18.125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="23.625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="33.25" style="6" customWidth="1"/>
     <col min="7" max="7" width="53.875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="27.5" style="6" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="6" customWidth="1"/>
     <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
@@ -2705,16 +3013,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="40.5">
       <c r="A3" s="4" t="s">
@@ -2727,7 +3035,7 @@
         <v>34</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
@@ -2745,7 +3053,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>58</v>
@@ -2775,7 +3083,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -2843,7 +3151,7 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>65</v>
@@ -2855,7 +3163,7 @@
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
       <c r="D12" s="13" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
@@ -2875,7 +3183,7 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>61</v>
@@ -2896,7 +3204,7 @@
         <v>59</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H14" s="7"/>
     </row>
@@ -2907,7 +3215,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>62</v>
@@ -2919,7 +3227,7 @@
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
       <c r="D16" s="13" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
@@ -2937,7 +3245,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -2945,40 +3253,40 @@
     <row r="18" spans="1:8" ht="54">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21" t="s">
+      <c r="C18" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18" t="s">
         <v>59</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" ht="27">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21" t="s">
+      <c r="C19" s="17"/>
+      <c r="D19" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" ht="40.5">
       <c r="A20" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
@@ -2987,7 +3295,7 @@
         <v>34</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
@@ -3005,7 +3313,7 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -3045,7 +3353,7 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="12" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7" t="s">
@@ -3059,7 +3367,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -3073,7 +3381,7 @@
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>89</v>
@@ -3089,13 +3397,13 @@
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27">
@@ -3105,7 +3413,7 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="13" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>83</v>
@@ -3133,7 +3441,7 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>64</v>
@@ -3147,7 +3455,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="15" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>84</v>
@@ -3161,7 +3469,7 @@
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>65</v>
@@ -3177,7 +3485,7 @@
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>92</v>
@@ -3193,7 +3501,7 @@
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>61</v>
@@ -3211,7 +3519,7 @@
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
@@ -3223,7 +3531,7 @@
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
@@ -3237,7 +3545,7 @@
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>96</v>
@@ -3253,7 +3561,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>63</v>
@@ -3263,15 +3571,15 @@
     <row r="39" spans="1:8" ht="40.5">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18" t="s">
         <v>143</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21" t="s">
-        <v>150</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
@@ -3279,13 +3587,13 @@
     <row r="40" spans="1:8">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21" t="s">
-        <v>165</v>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18" t="s">
+        <v>158</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -3301,14 +3609,14 @@
         <v>34</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H41" s="11"/>
     </row>
@@ -3319,7 +3627,7 @@
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
@@ -3333,7 +3641,7 @@
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -3345,7 +3653,7 @@
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
@@ -3357,7 +3665,7 @@
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="14" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
@@ -3367,11 +3675,11 @@
       <c r="B46" s="7"/>
       <c r="C46" s="8"/>
       <c r="D46" s="13" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7" t="s">
@@ -3385,7 +3693,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
@@ -3399,7 +3707,7 @@
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -3411,7 +3719,7 @@
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>64</v>
@@ -3425,7 +3733,7 @@
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="12" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -3437,7 +3745,7 @@
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>65</v>
@@ -3453,7 +3761,7 @@
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>57</v>
@@ -3469,7 +3777,7 @@
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>61</v>
@@ -3487,7 +3795,7 @@
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="12" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -3499,7 +3807,7 @@
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
@@ -3511,7 +3819,7 @@
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -3525,7 +3833,7 @@
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7" t="s">
@@ -3539,7 +3847,7 @@
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -3547,15 +3855,15 @@
     <row r="59" spans="1:8" ht="40.5">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
-      <c r="C59" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21" t="s">
+      <c r="C59" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D59" s="18" t="s">
         <v>137</v>
+      </c>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
@@ -3563,20 +3871,20 @@
     <row r="60" spans="1:8">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21" t="s">
-        <v>137</v>
+      <c r="C60" s="17"/>
+      <c r="D60" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
     <row r="61" spans="1:8" ht="40.5">
       <c r="A61" s="4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>10</v>
@@ -3603,7 +3911,7 @@
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -3615,7 +3923,7 @@
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -3629,7 +3937,7 @@
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -3641,7 +3949,7 @@
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
@@ -3651,11 +3959,11 @@
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
       <c r="D66" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
@@ -3667,7 +3975,7 @@
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -3681,7 +3989,7 @@
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -3693,7 +4001,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -3707,7 +4015,7 @@
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -3719,7 +4027,7 @@
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -3733,7 +4041,7 @@
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -3745,7 +4053,7 @@
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -3759,7 +4067,7 @@
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
@@ -3771,7 +4079,7 @@
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
@@ -3785,7 +4093,7 @@
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
@@ -3797,7 +4105,7 @@
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
@@ -3809,11 +4117,11 @@
         <v>25</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>36</v>
@@ -3831,7 +4139,7 @@
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>37</v>
@@ -3847,7 +4155,7 @@
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -3861,7 +4169,7 @@
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="13" t="s">
@@ -3871,15 +4179,15 @@
     <row r="82" spans="1:8" ht="40.5">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D82" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21" t="s">
-        <v>186</v>
+      <c r="C82" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18" t="s">
+        <v>179</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
@@ -3887,11 +4195,11 @@
     <row r="83" spans="1:8">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21" t="s">
-        <v>186</v>
+      <c r="C83" s="17"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18" t="s">
+        <v>179</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
@@ -3963,7 +4271,7 @@
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
@@ -4003,7 +4311,7 @@
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
@@ -4107,7 +4415,7 @@
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>36</v>
@@ -4135,14 +4443,14 @@
     <row r="101" spans="1:8" ht="40.5">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
-      <c r="C101" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D101" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21" t="s">
+      <c r="C101" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D101" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E101" s="18"/>
+      <c r="F101" s="18" t="s">
         <v>108</v>
       </c>
       <c r="G101" s="7"/>
@@ -4151,20 +4459,20 @@
     <row r="102" spans="1:8">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
-      <c r="C102" s="20"/>
-      <c r="D102" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21" t="s">
-        <v>166</v>
+      <c r="C102" s="17"/>
+      <c r="D102" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E102" s="18"/>
+      <c r="F102" s="18" t="s">
+        <v>159</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
     </row>
     <row r="103" spans="1:8" ht="40.5">
       <c r="A103" s="4" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>10</v>
@@ -4177,7 +4485,7 @@
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>45</v>
@@ -4205,7 +4513,7 @@
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
@@ -4215,7 +4523,7 @@
       <c r="B106" s="7"/>
       <c r="C106" s="8"/>
       <c r="D106" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
@@ -4273,7 +4581,7 @@
         <v>25</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7" t="s">
@@ -4335,7 +4643,7 @@
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="7" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
@@ -4349,7 +4657,7 @@
       </c>
       <c r="E115" s="7"/>
       <c r="F115" s="7" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
@@ -4361,7 +4669,7 @@
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
       <c r="F116" s="7" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
@@ -4384,10 +4692,10 @@
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="8" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7" t="s">
@@ -4403,7 +4711,7 @@
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
       <c r="F119" s="7" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
@@ -4413,11 +4721,11 @@
       <c r="B120" s="7"/>
       <c r="C120" s="8"/>
       <c r="D120" s="7" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
@@ -4429,7 +4737,7 @@
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
       <c r="F121" s="7" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
@@ -4449,7 +4757,7 @@
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="4" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G122" s="4" t="s">
         <v>30</v>
@@ -4499,7 +4807,7 @@
       <c r="B126" s="7"/>
       <c r="C126" s="8"/>
       <c r="D126" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E126" s="7"/>
       <c r="F126" s="7" t="s">
@@ -4605,11 +4913,11 @@
         <v>25</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="7" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G134" s="7" t="s">
         <v>36</v>
@@ -4625,7 +4933,7 @@
       </c>
       <c r="E135" s="7"/>
       <c r="F135" s="7" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>37</v>
@@ -4669,7 +4977,7 @@
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="7" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G138" s="7"/>
       <c r="H138" s="7"/>
@@ -4692,10 +5000,10 @@
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="8" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="7" t="s">
@@ -4709,18 +5017,18 @@
       <c r="B141" s="7"/>
       <c r="C141" s="8"/>
       <c r="D141" s="7" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="7" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G141" s="7"/>
       <c r="H141" s="7"/>
     </row>
     <row r="142" spans="1:8" ht="40.5">
       <c r="A142" s="4" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>10</v>
@@ -4803,7 +5111,7 @@
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
       <c r="F147" s="7" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G147" s="7"/>
       <c r="H147" s="7"/>
@@ -4844,369 +5152,390 @@
       <c r="G150" s="7"/>
       <c r="H150" s="7"/>
     </row>
-    <row r="151" spans="1:8" ht="54">
+    <row r="151" spans="1:8" ht="25.5" customHeight="1">
       <c r="A151" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C151" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D151" s="4"/>
-      <c r="E151" s="11"/>
-      <c r="F151" s="4"/>
+      <c r="C151" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E151" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>187</v>
+      </c>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
     </row>
-    <row r="152" spans="1:8">
-      <c r="A152" s="7"/>
-      <c r="B152" s="7"/>
-      <c r="C152" s="8"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
-      <c r="G152" s="7"/>
-      <c r="H152" s="7"/>
-    </row>
-    <row r="153" spans="1:8" ht="27">
-      <c r="A153" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C153" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D153" s="4"/>
-      <c r="E153" s="11"/>
-      <c r="F153" s="4"/>
-      <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
-    </row>
-    <row r="154" spans="1:8">
+    <row r="152" spans="1:8" s="3" customFormat="1" ht="31.5" customHeight="1">
+      <c r="A152" s="22"/>
+      <c r="B152" s="22"/>
+      <c r="C152" s="23"/>
+      <c r="D152" s="22"/>
+      <c r="E152" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="F152" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="G152" s="22"/>
+      <c r="H152" s="22"/>
+    </row>
+    <row r="153" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A153" s="7"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="8"/>
+      <c r="D153" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E153" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="F153" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
+    </row>
+    <row r="154" spans="1:8" ht="31.5" customHeight="1">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="8"/>
       <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
-      <c r="F154" s="7"/>
+      <c r="E154" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="F154" s="22" t="s">
+        <v>194</v>
+      </c>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
     </row>
-    <row r="155" spans="1:8" ht="27">
-      <c r="A155" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C155" s="11"/>
-      <c r="D155" s="4"/>
-      <c r="E155" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F155" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G155" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H155" s="4"/>
-    </row>
-    <row r="156" spans="1:8" ht="27">
+    <row r="155" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A155" s="7"/>
+      <c r="B155" s="7"/>
+      <c r="C155" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E155" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+    </row>
+    <row r="156" spans="1:8" ht="31.5" customHeight="1">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="8"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>133</v>
-      </c>
+      <c r="D156" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E156" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F156" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="G156" s="7"/>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" ht="31.5" customHeight="1">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
       <c r="C157" s="8"/>
       <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="E157" s="15"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
       <c r="H157" s="7"/>
     </row>
-    <row r="158" spans="1:8">
-      <c r="A158" s="7"/>
-      <c r="B158" s="7"/>
-      <c r="C158" s="8"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H158" s="7"/>
-    </row>
-    <row r="159" spans="1:8">
+    <row r="158" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A158" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E158" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="F158" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="H158" s="4"/>
+    </row>
+    <row r="159" spans="1:8" ht="31.5" customHeight="1">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
-      <c r="C159" s="8"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="G159" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="C159" s="23"/>
+      <c r="D159" s="22"/>
+      <c r="E159" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="F159" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="G159" s="7"/>
       <c r="H159" s="7"/>
     </row>
-    <row r="160" spans="1:8" ht="27">
-      <c r="A160" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C160" s="11"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F160" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G160" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H160" s="4"/>
-    </row>
-    <row r="161" spans="1:8">
+    <row r="160" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A160" s="7"/>
+      <c r="B160" s="7"/>
+      <c r="C160" s="8"/>
+      <c r="D160" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E160" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="F160" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
+    </row>
+    <row r="161" spans="1:8" ht="31.5" customHeight="1">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
       <c r="C161" s="8"/>
       <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G161" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="E161" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="F161" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="G161" s="7"/>
       <c r="H161" s="7"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" ht="31.5" customHeight="1">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
-      <c r="C162" s="8"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G162" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="C162" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E162" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="F162" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="G162" s="7"/>
       <c r="H162" s="7"/>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" ht="31.5" customHeight="1">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
       <c r="C163" s="8"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="G163" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="D163" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E163" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="F163" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G163" s="7"/>
       <c r="H163" s="7"/>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" ht="31.5" customHeight="1">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="8"/>
       <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
-      <c r="F164" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="G164" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="E164" s="15"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="7"/>
       <c r="H164" s="7"/>
     </row>
-    <row r="165" spans="1:8" ht="39" customHeight="1">
+    <row r="165" spans="1:8" ht="26.25" customHeight="1">
       <c r="A165" s="4" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C165" s="11" t="s">
-        <v>121</v>
+        <v>7</v>
+      </c>
+      <c r="C165" s="16" t="s">
+        <v>203</v>
       </c>
       <c r="D165" s="4"/>
-      <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
-      <c r="G165" s="4"/>
+      <c r="E165" s="16"/>
+      <c r="F165" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="G165" s="16" t="s">
+        <v>126</v>
+      </c>
       <c r="H165" s="4"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" ht="26.25" customHeight="1">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
-      <c r="C166" s="8"/>
+      <c r="C166" s="8" t="s">
+        <v>204</v>
+      </c>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
+      <c r="F166" s="7" t="s">
+        <v>207</v>
+      </c>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
     </row>
-    <row r="167" spans="1:8" ht="54">
-      <c r="A167" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D167" s="5"/>
-      <c r="E167" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F167" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G167" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="H167" s="4"/>
-    </row>
-    <row r="168" spans="1:8" ht="27">
-      <c r="A168" s="8"/>
-      <c r="B168" s="8"/>
+    <row r="167" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A167" s="7"/>
+      <c r="B167" s="7"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G167" s="7"/>
+      <c r="H167" s="7"/>
+    </row>
+    <row r="168" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A168" s="7"/>
+      <c r="B168" s="7"/>
       <c r="C168" s="8"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
-      <c r="F168" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G168" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="F168" s="7"/>
+      <c r="G168" s="7"/>
       <c r="H168" s="7"/>
     </row>
-    <row r="169" spans="1:8" ht="27">
-      <c r="A169" s="8"/>
-      <c r="B169" s="8"/>
-      <c r="C169" s="8"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G169" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H169" s="7"/>
-    </row>
-    <row r="170" spans="1:8" ht="27">
-      <c r="A170" s="8"/>
-      <c r="B170" s="8"/>
+    <row r="169" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A169" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D169" s="4"/>
+      <c r="E169" s="16"/>
+      <c r="F169" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="G169" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H169" s="4"/>
+    </row>
+    <row r="170" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A170" s="7"/>
+      <c r="B170" s="7"/>
       <c r="C170" s="8"/>
       <c r="D170" s="7"/>
-      <c r="E170" s="7" t="s">
-        <v>53</v>
-      </c>
+      <c r="E170" s="7"/>
       <c r="F170" s="7" t="s">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="H170" s="7"/>
     </row>
-    <row r="171" spans="1:8">
-      <c r="A171" s="8"/>
-      <c r="B171" s="8"/>
-      <c r="C171" s="8"/>
+    <row r="171" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A171" s="7"/>
+      <c r="B171" s="7"/>
+      <c r="C171" s="8" t="s">
+        <v>204</v>
+      </c>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
-      <c r="F171" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G171" s="7"/>
+      <c r="F171" s="7" t="s">
+        <v>209</v>
+      </c>
       <c r="H171" s="7"/>
     </row>
-    <row r="172" spans="1:8" ht="27">
-      <c r="A172" s="8"/>
-      <c r="B172" s="8"/>
+    <row r="172" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A172" s="7"/>
+      <c r="B172" s="7"/>
       <c r="C172" s="8"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
       <c r="F172" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G172" s="7"/>
       <c r="H172" s="7"/>
     </row>
-    <row r="173" spans="1:8" ht="27">
-      <c r="A173" s="8"/>
-      <c r="B173" s="8"/>
-      <c r="C173" s="8"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G173" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H173" s="7"/>
-    </row>
-    <row r="174" spans="1:8" ht="40.5">
-      <c r="A174" s="8"/>
-      <c r="B174" s="8"/>
-      <c r="C174" s="8" t="s">
-        <v>50</v>
-      </c>
+    <row r="173" spans="1:8" ht="39" customHeight="1">
+      <c r="A173" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C173" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D173" s="4"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4"/>
+      <c r="G173" s="4"/>
+      <c r="H173" s="4"/>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="7"/>
+      <c r="B174" s="7"/>
+      <c r="C174" s="8"/>
       <c r="D174" s="7"/>
-      <c r="E174" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F174" s="7" t="s">
-        <v>163</v>
-      </c>
+      <c r="E174" s="7"/>
+      <c r="F174" s="7"/>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
     </row>
-    <row r="175" spans="1:8" ht="27">
-      <c r="A175" s="8"/>
-      <c r="B175" s="8"/>
-      <c r="C175" s="8"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G175" s="7"/>
-      <c r="H175" s="7"/>
+    <row r="175" spans="1:8" ht="54">
+      <c r="A175" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D175" s="5"/>
+      <c r="E175" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H175" s="4"/>
     </row>
     <row r="176" spans="1:8" ht="27">
       <c r="A176" s="8"/>
@@ -5214,189 +5543,301 @@
       <c r="C176" s="8"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
-      <c r="F176" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G176" s="7"/>
+      <c r="F176" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="H176" s="7"/>
     </row>
-    <row r="177" spans="1:8" ht="40.5">
-      <c r="A177" s="7"/>
-      <c r="B177" s="7"/>
-      <c r="C177" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D177" s="7" t="s">
-        <v>144</v>
-      </c>
+    <row r="177" spans="1:8" ht="27">
+      <c r="A177" s="8"/>
+      <c r="B177" s="8"/>
+      <c r="C177" s="8"/>
+      <c r="D177" s="7"/>
       <c r="E177" s="7"/>
-      <c r="F177" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="G177" s="7"/>
+      <c r="F177" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G177" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="H177" s="7"/>
     </row>
     <row r="178" spans="1:8" ht="27">
-      <c r="A178" s="7"/>
-      <c r="B178" s="7"/>
+      <c r="A178" s="8"/>
+      <c r="B178" s="8"/>
       <c r="C178" s="8"/>
       <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
+      <c r="E178" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="F178" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G178" s="7"/>
+        <v>80</v>
+      </c>
+      <c r="G178" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="H178" s="7"/>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="7"/>
-      <c r="B179" s="7"/>
+      <c r="A179" s="8"/>
+      <c r="B179" s="8"/>
       <c r="C179" s="8"/>
-      <c r="D179" s="7" t="s">
-        <v>145</v>
-      </c>
+      <c r="D179" s="7"/>
       <c r="E179" s="7"/>
-      <c r="F179" s="7" t="s">
-        <v>163</v>
+      <c r="F179" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="G179" s="7"/>
       <c r="H179" s="7"/>
     </row>
     <row r="180" spans="1:8" ht="27">
-      <c r="A180" s="7"/>
-      <c r="B180" s="7"/>
+      <c r="A180" s="8"/>
+      <c r="B180" s="8"/>
       <c r="C180" s="8"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
       <c r="F180" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G180" s="7"/>
+        <v>173</v>
+      </c>
+      <c r="G180" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="H180" s="7"/>
     </row>
-    <row r="181" spans="1:8" ht="40.5">
-      <c r="A181" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D181" s="5"/>
-      <c r="E181" s="4"/>
-      <c r="F181" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="G181" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H181" s="4"/>
-    </row>
-    <row r="182" spans="1:8" ht="27">
-      <c r="A182" s="7"/>
-      <c r="B182" s="7"/>
-      <c r="C182" s="8"/>
+    <row r="181" spans="1:8" ht="27">
+      <c r="A181" s="8"/>
+      <c r="B181" s="8"/>
+      <c r="C181" s="8"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="7"/>
+      <c r="F181" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G181" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="H181" s="7"/>
+    </row>
+    <row r="182" spans="1:8" ht="40.5">
+      <c r="A182" s="8"/>
+      <c r="B182" s="8"/>
+      <c r="C182" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
+      <c r="E182" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="F182" s="7" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
     </row>
     <row r="183" spans="1:8" ht="27">
-      <c r="A183" s="7"/>
-      <c r="B183" s="7"/>
+      <c r="A183" s="8"/>
+      <c r="B183" s="8"/>
       <c r="C183" s="8"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
       <c r="F183" s="7" t="s">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
     </row>
     <row r="184" spans="1:8" ht="27">
-      <c r="A184" s="7"/>
-      <c r="B184" s="7"/>
-      <c r="C184" s="8" t="s">
-        <v>191</v>
-      </c>
+      <c r="A184" s="8"/>
+      <c r="B184" s="8"/>
+      <c r="C184" s="8"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
-      <c r="F184" s="7" t="s">
-        <v>190</v>
+      <c r="F184" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
     </row>
     <row r="185" spans="1:8" ht="40.5">
-      <c r="A185" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D185" s="5"/>
-      <c r="E185" s="4"/>
-      <c r="F185" s="4"/>
-      <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
-    </row>
-    <row r="186" spans="1:8">
+      <c r="A185" s="7"/>
+      <c r="B185" s="7"/>
+      <c r="C185" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E185" s="7"/>
+      <c r="F185" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G185" s="7"/>
+      <c r="H185" s="7"/>
+    </row>
+    <row r="186" spans="1:8" ht="27">
+      <c r="A186" s="7"/>
+      <c r="B186" s="7"/>
       <c r="C186" s="8"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
-      <c r="F186" s="7"/>
+      <c r="F186" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="G186" s="7"/>
       <c r="H186" s="7"/>
     </row>
-    <row r="187" spans="1:8" ht="40.5">
-      <c r="A187" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D187" s="4"/>
-      <c r="E187" s="4"/>
-      <c r="F187" s="4"/>
-      <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
-    </row>
-    <row r="188" spans="1:8">
-      <c r="A188" s="8"/>
-      <c r="B188" s="8"/>
+    <row r="187" spans="1:8">
+      <c r="A187" s="7"/>
+      <c r="B187" s="7"/>
+      <c r="C187" s="8"/>
+      <c r="D187" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G187" s="7"/>
+      <c r="H187" s="7"/>
+    </row>
+    <row r="188" spans="1:8" ht="27">
+      <c r="A188" s="7"/>
+      <c r="B188" s="7"/>
       <c r="C188" s="8"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
-      <c r="F188" s="7"/>
+      <c r="F188" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
     </row>
-    <row r="189" spans="1:8">
-      <c r="A189" s="8"/>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
-      <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
-      <c r="G189" s="7"/>
-      <c r="H189" s="7"/>
-    </row>
-    <row r="190" spans="1:8">
-      <c r="D190" s="9"/>
-      <c r="E190" s="9"/>
-      <c r="F190" s="9"/>
-      <c r="G190" s="9"/>
+    <row r="189" spans="1:8" ht="40.5">
+      <c r="A189" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D189" s="5"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G189" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H189" s="4"/>
+    </row>
+    <row r="190" spans="1:8" ht="27">
+      <c r="A190" s="7"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="8"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
+    </row>
+    <row r="191" spans="1:8" ht="27">
+      <c r="A191" s="7"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="8"/>
+      <c r="D191" s="7"/>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="G191" s="7"/>
+      <c r="H191" s="7"/>
+    </row>
+    <row r="192" spans="1:8" ht="27">
+      <c r="A192" s="7"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D192" s="7"/>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="G192" s="7"/>
+      <c r="H192" s="7"/>
+    </row>
+    <row r="193" spans="1:8" ht="40.5">
+      <c r="A193" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D193" s="5"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4"/>
+      <c r="G193" s="4"/>
+      <c r="H193" s="4"/>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="C194" s="8"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
+      <c r="G194" s="7"/>
+      <c r="H194" s="7"/>
+    </row>
+    <row r="195" spans="1:8" ht="40.5">
+      <c r="A195" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
+      <c r="G195" s="4"/>
+      <c r="H195" s="4"/>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" s="8"/>
+      <c r="B196" s="8"/>
+      <c r="C196" s="8"/>
+      <c r="D196" s="7"/>
+      <c r="E196" s="7"/>
+      <c r="F196" s="7"/>
+      <c r="G196" s="7"/>
+      <c r="H196" s="7"/>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" s="8"/>
+      <c r="B197" s="8"/>
+      <c r="C197" s="8"/>
+      <c r="D197" s="7"/>
+      <c r="E197" s="7"/>
+      <c r="F197" s="7"/>
+      <c r="G197" s="7"/>
+      <c r="H197" s="7"/>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="D198" s="9"/>
+      <c r="E198" s="9"/>
+      <c r="F198" s="9"/>
+      <c r="G198" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H100">

--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试/集群管理故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试/集群管理故障测试设计_review.xlsx
@@ -1018,7 +1018,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A165" authorId="0">
+    <comment ref="A179" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1042,6 +1042,58 @@
           <t xml:space="preserve">
 1、节点运行时coord、data主机重启在基本操作中已有覆盖
 2、主机正常/异常重启的设计只做简单覆盖，不像节点正常/异常重启那么详细</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E192" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+确认下能不能测这个用例</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+确认下能不能测这个用例</t>
         </r>
       </text>
     </comment>
@@ -1050,7 +1102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="220">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1247,38 +1299,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM异常停止（kill -9）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复多次创建删除不同coord组和节点/catalog组和节点/dataRG和节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>启停节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>时间跳变+catalog主节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反复多次启停coord节点、catalog节点、dataRG节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改一个主机的hostname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点连续降备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建/删除成功；故障恢复后各个节点数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>操作过程中异常，cataRG创建失败；故障恢复后创建成功的cataRG正常可用，在cataRG创建catalog节点创建成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1327,10 +1351,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>集群管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1339,18 +1359,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>进程退出，操作失败；CM重启完成后可以继续创建/删除节点组和节点，节点可以正常使用；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作失败；故障恢复后可以继续创建/删除节点组和节点，节点可以正常使用；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM跟该主机通信失败，操作失败；故障恢复后主机可以正常连接，节点间信息正常同步，同步后数据完整一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>catalog备节点断网</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1371,15 +1379,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM进程挂死</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主机hostname/IP更改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM异常停止（kill -9 kill -15重复操作）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1933,10 +1933,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>节点异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>集群管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1949,10 +1945,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建组和节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>磁盘损坏（低优先级）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1966,10 +1958,6 @@
   </si>
   <si>
     <t>主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重启后CM和节点会自动拉起，拉起后各节点运行正常,对节点做基本操作，操作成功（如连接coord做数据操作）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2157,22 +2145,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>少于(n+1/2)个catalog备节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>超过(n+1/2)个catalog备节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>进程退出，操作失败；CM重启完成后可以继续创建/删除节点组和节点；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建/删除失败；故障恢复后再次创建/删除成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>catalog主节点所在主机CPU耗尽</t>
   </si>
   <si>
@@ -2208,38 +2184,45 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>coord正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cata主节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataRG时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除dataRG时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord异常重启</t>
+  </si>
+  <si>
+    <t>cata主节点异常重启</t>
+  </si>
+  <si>
     <t>创建/删除节点组和节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建dataRG时连接的coord正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord正常重启</t>
-  </si>
-  <si>
-    <t>coord正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cata主节点正常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建dataRG时cata主节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建dataRG时</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除dataRG时</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除dataRG时cata主节点正常重启</t>
+    <t>创建coord节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm进程正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建data节点时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2251,86 +2234,162 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>启动data节点时连接的coord正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>停止data节点时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>attach cata节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detach 备份节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cata节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建data节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm进程异常重启</t>
+  </si>
+  <si>
+    <t>data节点正常停止</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cataRG时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除data节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord正常重启和异常重启一样，作交叉覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm正常重启和异常重启一样，作交叉覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>coord异常重启</t>
-  </si>
-  <si>
-    <t>cata主节点异常重启</t>
-  </si>
-  <si>
-    <t>创建dataRG时cata主节点异常重启</t>
-  </si>
-  <si>
-    <t>删除dataRG时cata主节点异常重启</t>
-  </si>
-  <si>
-    <t>节点运行过程中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建/删除节点组和节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点所在主机正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点所在主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建dataRG时目标节点所在主机正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建dataRG时cata主节点所在主机正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建cataRG时目标节点所在主机异常重启</t>
-  </si>
-  <si>
-    <t>创建dataRG时cata主节点所在主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除dataRG时连接的coord正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停止data节点时连接的coord正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动data节点时连接的coord异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除dataRG时连接的coord异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建dataRG时连接的coord异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点所在主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>预期结果：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停止data节点时连接的coord异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm进程正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detach data节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attach 备份节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm进程异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除cata节点时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataNode时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除dataNode时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cata主节点主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cataNode时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点/cm异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点/cm正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机异常只作简单设计，不作详细设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cata主节点主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时创建cata节点和数据节点，cata节点升主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发创建删除不同coord节点catalog节点data节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发启停coord节点、catalog节点、dataRG节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建数据组时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除dataRG(组上有节点)时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多次detach/attach时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点连续降备</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2586,6 +2645,15 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2595,16 +2663,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2972,7 +3031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2982,7 +3041,7 @@
     <col min="5" max="5" width="18.125" style="6" customWidth="1"/>
     <col min="6" max="6" width="33.25" style="6" customWidth="1"/>
     <col min="7" max="7" width="53.875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="12.625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="28.5" style="6" customWidth="1"/>
     <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
@@ -3013,18 +3072,18 @@
       </c>
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="40.5">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="24"/>
+    </row>
+    <row r="3" spans="1:8" ht="27">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -3035,14 +3094,14 @@
         <v>34</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H3" s="11"/>
     </row>
@@ -3053,14 +3112,14 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" ht="27">
+    <row r="5" spans="1:8" ht="54">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
@@ -3073,7 +3132,7 @@
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3083,7 +3142,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -3095,10 +3154,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="H7" s="7"/>
     </row>
@@ -3123,10 +3182,10 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H9" s="7"/>
     </row>
@@ -3137,10 +3196,10 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="15" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -3151,29 +3210,29 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:8" ht="27">
+    <row r="12" spans="1:8" ht="54">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
       <c r="D12" s="13" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27">
@@ -3183,10 +3242,10 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H13" s="7"/>
     </row>
@@ -3194,17 +3253,17 @@
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H14" s="7"/>
     </row>
@@ -3215,19 +3274,19 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" ht="27">
+    <row r="16" spans="1:8" ht="54">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
       <c r="D16" s="13" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
@@ -3235,7 +3294,7 @@
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3245,7 +3304,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -3254,17 +3313,17 @@
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="17" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="18" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="H18" s="7"/>
     </row>
@@ -3273,20 +3332,20 @@
       <c r="B19" s="7"/>
       <c r="C19" s="17"/>
       <c r="D19" s="18" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="18" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" ht="40.5">
+    <row r="20" spans="1:8" ht="27">
       <c r="A20" s="4" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
@@ -3295,7 +3354,7 @@
         <v>34</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
@@ -3313,7 +3372,7 @@
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -3323,7 +3382,7 @@
       <c r="B22" s="7"/>
       <c r="C22" s="8"/>
       <c r="D22" s="7" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>31</v>
@@ -3346,14 +3405,14 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" ht="27">
+    <row r="24" spans="1:8" ht="54">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="8"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="12" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7" t="s">
@@ -3367,12 +3426,12 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" ht="27">
+    <row r="26" spans="1:8" ht="54">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="8"/>
@@ -3381,29 +3440,29 @@
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="13" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="54">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="108">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="8"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27">
@@ -3413,10 +3472,10 @@
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="13" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H28" s="7"/>
     </row>
@@ -3441,10 +3500,10 @@
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H30" s="7"/>
     </row>
@@ -3455,10 +3514,10 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="15" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H31" s="7"/>
     </row>
@@ -3469,29 +3528,29 @@
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" ht="27">
+    <row r="33" spans="1:8" ht="54">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
       <c r="D33" s="13" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="27">
@@ -3501,10 +3560,10 @@
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H34" s="7"/>
     </row>
@@ -3512,14 +3571,14 @@
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
@@ -3531,12 +3590,12 @@
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" ht="27">
+    <row r="37" spans="1:8" ht="54">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="8"/>
@@ -3545,13 +3604,13 @@
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27">
@@ -3561,25 +3620,25 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" ht="40.5">
+    <row r="39" spans="1:8" ht="27">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="17" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39" s="18" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
@@ -3589,11 +3648,11 @@
       <c r="B40" s="7"/>
       <c r="C40" s="17"/>
       <c r="D40" s="18" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E40" s="18"/>
       <c r="F40" s="18" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -3609,14 +3668,14 @@
         <v>34</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="H41" s="11"/>
     </row>
@@ -3627,7 +3686,7 @@
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
@@ -3641,7 +3700,7 @@
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -3653,7 +3712,7 @@
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
@@ -3665,25 +3724,25 @@
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="14" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8" ht="27">
+    <row r="46" spans="1:8" ht="40.5">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="8"/>
       <c r="D46" s="13" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -3693,7 +3752,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
@@ -3703,11 +3762,11 @@
       <c r="B48" s="7"/>
       <c r="C48" s="8"/>
       <c r="D48" s="7" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -3719,10 +3778,10 @@
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H49" s="7"/>
     </row>
@@ -3733,7 +3792,7 @@
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="12" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -3745,29 +3804,29 @@
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" ht="27">
+    <row r="52" spans="1:8" ht="40.5">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
       <c r="D52" s="13" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="27">
@@ -3777,25 +3836,25 @@
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" ht="27">
+    <row r="54" spans="1:8">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="12" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -3807,7 +3866,7 @@
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
@@ -3819,25 +3878,25 @@
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
     </row>
-    <row r="57" spans="1:8" ht="27">
+    <row r="57" spans="1:8" ht="54">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8"/>
       <c r="D57" s="13" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -3847,23 +3906,23 @@
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
     </row>
-    <row r="59" spans="1:8" ht="40.5">
+    <row r="59" spans="1:8" ht="27">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="17" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E59" s="18"/>
       <c r="F59" s="18" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
@@ -3873,18 +3932,18 @@
       <c r="B60" s="7"/>
       <c r="C60" s="17"/>
       <c r="D60" s="18" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E60" s="18"/>
       <c r="F60" s="18" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
     <row r="61" spans="1:8" ht="40.5">
       <c r="A61" s="4" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>10</v>
@@ -3904,14 +3963,14 @@
       </c>
       <c r="H61" s="4"/>
     </row>
-    <row r="62" spans="1:8" ht="27">
+    <row r="62" spans="1:8">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -3923,21 +3982,21 @@
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" ht="27">
+    <row r="64" spans="1:8">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="8"/>
       <c r="D64" s="7" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -3949,21 +4008,21 @@
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" ht="27">
+    <row r="66" spans="1:8">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
       <c r="D66" s="7" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
@@ -3975,7 +4034,7 @@
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -3989,7 +4048,7 @@
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -4001,7 +4060,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -4011,11 +4070,11 @@
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
       <c r="D70" s="13" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -4027,12 +4086,12 @@
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8" ht="27">
+    <row r="72" spans="1:8">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="8"/>
@@ -4041,7 +4100,7 @@
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -4053,12 +4112,12 @@
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" ht="27">
+    <row r="74" spans="1:8">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="8"/>
@@ -4067,7 +4126,7 @@
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
@@ -4079,7 +4138,7 @@
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
@@ -4093,7 +4152,7 @@
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="7" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
@@ -4105,29 +4164,29 @@
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" ht="40.5">
+    <row r="78" spans="1:8" ht="67.5">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>36</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -4135,11 +4194,11 @@
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
       <c r="D79" s="7" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>37</v>
@@ -4155,12 +4214,12 @@
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27">
+    <row r="81" spans="1:8" ht="54">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="8"/>
@@ -4169,25 +4228,25 @@
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="40.5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="27">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="17" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D82" s="18" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E82" s="18"/>
       <c r="F82" s="18" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
@@ -4199,7 +4258,7 @@
       <c r="D83" s="18"/>
       <c r="E83" s="18"/>
       <c r="F83" s="18" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
@@ -4226,14 +4285,14 @@
       </c>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8" ht="27">
+    <row r="85" spans="1:8">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="8"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
@@ -4245,21 +4304,21 @@
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" ht="27">
+    <row r="87" spans="1:8">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8"/>
       <c r="D87" s="7" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
@@ -4271,12 +4330,12 @@
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" ht="27">
+    <row r="89" spans="1:8">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
@@ -4285,7 +4344,7 @@
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
@@ -4297,7 +4356,7 @@
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
@@ -4311,7 +4370,7 @@
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
@@ -4323,7 +4382,7 @@
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
@@ -4333,11 +4392,11 @@
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
       <c r="D93" s="13" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
@@ -4349,12 +4408,12 @@
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="7" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
     </row>
-    <row r="95" spans="1:8" ht="27">
+    <row r="95" spans="1:8">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="8"/>
@@ -4363,7 +4422,7 @@
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
@@ -4375,7 +4434,7 @@
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
@@ -4389,7 +4448,7 @@
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
@@ -4401,12 +4460,12 @@
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
       <c r="F98" s="7" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
     </row>
-    <row r="99" spans="1:8" ht="40.5">
+    <row r="99" spans="1:8" ht="67.5">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="8"/>
@@ -4415,13 +4474,13 @@
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>36</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -4433,25 +4492,25 @@
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="G100" s="7" t="s">
         <v>37</v>
       </c>
       <c r="H100" s="7"/>
     </row>
-    <row r="101" spans="1:8" ht="40.5">
+    <row r="101" spans="1:8" ht="27">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="17" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E101" s="18"/>
       <c r="F101" s="18" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
@@ -4461,18 +4520,18 @@
       <c r="B102" s="7"/>
       <c r="C102" s="17"/>
       <c r="D102" s="18" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E102" s="18"/>
       <c r="F102" s="18" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
     </row>
-    <row r="103" spans="1:8" ht="40.5">
+    <row r="103" spans="1:8" ht="27">
       <c r="A103" s="4" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>10</v>
@@ -4485,21 +4544,21 @@
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>45</v>
       </c>
       <c r="H103" s="4"/>
     </row>
-    <row r="104" spans="1:8" ht="27">
+    <row r="104" spans="1:8">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="8"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
@@ -4509,11 +4568,11 @@
       <c r="B105" s="7"/>
       <c r="C105" s="8"/>
       <c r="D105" s="7" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
@@ -4523,11 +4582,11 @@
       <c r="B106" s="7"/>
       <c r="C106" s="8"/>
       <c r="D106" s="7" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
@@ -4541,7 +4600,7 @@
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
@@ -4555,7 +4614,7 @@
       </c>
       <c r="E108" s="7"/>
       <c r="F108" s="7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
@@ -4569,23 +4628,23 @@
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
     </row>
-    <row r="110" spans="1:8" ht="27">
+    <row r="110" spans="1:8">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G110" s="7" t="s">
         <v>46</v>
@@ -4597,11 +4656,11 @@
       <c r="B111" s="7"/>
       <c r="C111" s="8"/>
       <c r="D111" s="7" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G111" s="7" t="s">
         <v>37</v>
@@ -4617,19 +4676,19 @@
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8" ht="27">
+    <row r="113" spans="1:8">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="8"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
       <c r="F113" s="7" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
@@ -4643,12 +4702,12 @@
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="7" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" ht="27">
+    <row r="115" spans="1:8">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="8"/>
@@ -4657,7 +4716,7 @@
       </c>
       <c r="E115" s="7"/>
       <c r="F115" s="7" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
@@ -4669,7 +4728,7 @@
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
       <c r="F116" s="7" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
@@ -4683,23 +4742,23 @@
       </c>
       <c r="E117" s="7"/>
       <c r="F117" s="7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" ht="40.5">
+    <row r="118" spans="1:8" ht="27">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="8" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
@@ -4711,21 +4770,21 @@
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
       <c r="F119" s="7" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" ht="27">
+    <row r="120" spans="1:8">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="8"/>
       <c r="D120" s="7" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
@@ -4737,7 +4796,7 @@
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
       <c r="F121" s="7" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
@@ -4757,35 +4816,35 @@
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="4" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="G122" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H122" s="4"/>
     </row>
-    <row r="123" spans="1:8" ht="27">
+    <row r="123" spans="1:8">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="8"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
       <c r="F123" s="7" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" ht="27">
+    <row r="124" spans="1:8">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="8"/>
       <c r="D124" s="7" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
@@ -4797,21 +4856,21 @@
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
     </row>
-    <row r="126" spans="1:8" ht="27">
+    <row r="126" spans="1:8">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="8"/>
       <c r="D126" s="7" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E126" s="7"/>
       <c r="F126" s="7" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
@@ -4823,7 +4882,7 @@
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
@@ -4837,7 +4896,7 @@
       </c>
       <c r="E128" s="7"/>
       <c r="F128" s="7" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="7"/>
@@ -4849,12 +4908,12 @@
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" ht="27">
+    <row r="130" spans="1:8">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="8"/>
@@ -4863,7 +4922,7 @@
       </c>
       <c r="E130" s="7"/>
       <c r="F130" s="7" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
@@ -4875,7 +4934,7 @@
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="7"/>
@@ -4889,7 +4948,7 @@
       </c>
       <c r="E132" s="7"/>
       <c r="F132" s="7" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
@@ -4901,7 +4960,7 @@
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
@@ -4913,11 +4972,11 @@
         <v>25</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="7" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="G134" s="7" t="s">
         <v>36</v>
@@ -4929,11 +4988,11 @@
       <c r="B135" s="7"/>
       <c r="C135" s="8"/>
       <c r="D135" s="7" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E135" s="7"/>
       <c r="F135" s="7" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>37</v>
@@ -4949,7 +5008,7 @@
       </c>
       <c r="E136" s="7"/>
       <c r="F136" s="7" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
@@ -4963,7 +5022,7 @@
       </c>
       <c r="E137" s="7"/>
       <c r="F137" s="7" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
@@ -4977,7 +5036,7 @@
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="7" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="G138" s="7"/>
       <c r="H138" s="7"/>
@@ -4991,23 +5050,23 @@
       </c>
       <c r="E139" s="7"/>
       <c r="F139" s="7" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G139" s="7"/>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" ht="40.5">
+    <row r="140" spans="1:8" ht="27">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="8" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G140" s="7"/>
       <c r="H140" s="7"/>
@@ -5017,38 +5076,38 @@
       <c r="B141" s="7"/>
       <c r="C141" s="8"/>
       <c r="D141" s="7" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="7" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G141" s="7"/>
       <c r="H141" s="7"/>
     </row>
     <row r="142" spans="1:8" ht="40.5">
       <c r="A142" s="4" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H142" s="4"/>
     </row>
-    <row r="143" spans="1:8" ht="27">
+    <row r="143" spans="1:8">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="8" t="s">
@@ -5099,7 +5158,7 @@
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
       <c r="F146" s="7" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="G146" s="7"/>
       <c r="H146" s="7"/>
@@ -5111,7 +5170,7 @@
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
       <c r="F147" s="7" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="G147" s="7"/>
       <c r="H147" s="7"/>
@@ -5123,7 +5182,7 @@
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
       <c r="F148" s="7" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="G148" s="7"/>
       <c r="H148" s="7"/>
@@ -5135,7 +5194,7 @@
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
       <c r="F149" s="7" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="G149" s="7"/>
       <c r="H149" s="7"/>
@@ -5147,60 +5206,58 @@
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
       <c r="F150" s="7" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="G150" s="7"/>
       <c r="H150" s="7"/>
     </row>
     <row r="151" spans="1:8" ht="25.5" customHeight="1">
       <c r="A151" s="4" t="s">
-        <v>68</v>
+        <v>205</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="E151" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="F151" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F151" s="4"/>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A152" s="7"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="8"/>
+      <c r="D152" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="G151" s="4"/>
-      <c r="H151" s="4"/>
-    </row>
-    <row r="152" spans="1:8" s="3" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A152" s="22"/>
-      <c r="B152" s="22"/>
-      <c r="C152" s="23"/>
-      <c r="D152" s="22"/>
-      <c r="E152" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="F152" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="G152" s="22"/>
-      <c r="H152" s="22"/>
+      <c r="E152" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F152" s="19"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
     </row>
     <row r="153" spans="1:8" ht="31.5" customHeight="1">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
       <c r="C153" s="8"/>
       <c r="D153" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E153" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="F153" s="14" t="s">
-        <v>211</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="E153" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F153" s="19"/>
       <c r="G153" s="7"/>
       <c r="H153" s="7"/>
     </row>
@@ -5208,13 +5265,13 @@
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="8"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="F154" s="22" t="s">
-        <v>194</v>
-      </c>
+      <c r="D154" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E154" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F154" s="19"/>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
     </row>
@@ -5222,16 +5279,13 @@
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="8" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E155" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F155" s="7" t="s">
-        <v>197</v>
+        <v>184</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="G155" s="7"/>
       <c r="H155" s="7"/>
@@ -5241,14 +5295,12 @@
       <c r="B156" s="7"/>
       <c r="C156" s="8"/>
       <c r="D156" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E156" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F156" s="14" t="s">
-        <v>212</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="E156" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F156" s="19"/>
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
     </row>
@@ -5256,62 +5308,60 @@
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
       <c r="C157" s="8"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="15"/>
-      <c r="F157" s="7"/>
+      <c r="D157" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="F157" s="19"/>
       <c r="G157" s="7"/>
       <c r="H157" s="7"/>
     </row>
     <row r="158" spans="1:8" ht="31.5" customHeight="1">
-      <c r="A158" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D158" s="4" t="s">
+      <c r="A158" s="7"/>
+      <c r="B158" s="7"/>
+      <c r="C158" s="8"/>
+      <c r="D158" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E158" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F158" s="7"/>
+      <c r="G158" s="7"/>
+      <c r="H158" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="E158" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F158" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="G158" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="H158" s="4"/>
     </row>
     <row r="159" spans="1:8" ht="31.5" customHeight="1">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
-      <c r="C159" s="23"/>
-      <c r="D159" s="22"/>
-      <c r="E159" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="F159" s="22" t="s">
-        <v>201</v>
-      </c>
+      <c r="C159" s="8"/>
+      <c r="D159" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E159" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F159" s="7"/>
       <c r="G159" s="7"/>
       <c r="H159" s="7"/>
     </row>
     <row r="160" spans="1:8" ht="31.5" customHeight="1">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
-      <c r="C160" s="8"/>
+      <c r="C160" s="8" t="s">
+        <v>178</v>
+      </c>
       <c r="D160" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E160" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="F160" s="22" t="s">
-        <v>214</v>
+        <v>179</v>
+      </c>
+      <c r="E160" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
@@ -5320,13 +5370,13 @@
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
       <c r="C161" s="8"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="F161" s="22" t="s">
-        <v>202</v>
-      </c>
+      <c r="D161" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E161" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F161" s="7"/>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
     </row>
@@ -5334,17 +5384,15 @@
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="8" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E162" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="F162" s="14" t="s">
-        <v>213</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="E162" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="F162" s="7"/>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
     </row>
@@ -5353,14 +5401,12 @@
       <c r="B163" s="7"/>
       <c r="C163" s="8"/>
       <c r="D163" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E163" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="F163" s="14" t="s">
-        <v>218</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="E163" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F163" s="7"/>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
     </row>
@@ -5369,475 +5415,569 @@
       <c r="B164" s="7"/>
       <c r="C164" s="8"/>
       <c r="D164" s="7"/>
-      <c r="E164" s="15"/>
+      <c r="E164" s="20"/>
       <c r="F164" s="7"/>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
     </row>
-    <row r="165" spans="1:8" ht="26.25" customHeight="1">
-      <c r="A165" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B165" s="4" t="s">
+    <row r="165" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A165" s="7"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="8"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="20"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="7"/>
+      <c r="H165" s="7"/>
+    </row>
+    <row r="166" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A166" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B166" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C165" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D165" s="4"/>
-      <c r="E165" s="16"/>
-      <c r="F165" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="G165" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H165" s="4"/>
-    </row>
-    <row r="166" spans="1:8" ht="26.25" customHeight="1">
-      <c r="A166" s="7"/>
-      <c r="B166" s="7"/>
-      <c r="C166" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="G166" s="7"/>
-      <c r="H166" s="7"/>
-    </row>
-    <row r="167" spans="1:8" ht="26.25" customHeight="1">
+      <c r="C166" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E166" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F166" s="4"/>
+      <c r="G166" s="4"/>
+      <c r="H166" s="4"/>
+    </row>
+    <row r="167" spans="1:8" ht="31.5" customHeight="1">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
       <c r="C167" s="8"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7" t="s">
-        <v>208</v>
-      </c>
+      <c r="D167" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E167" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F167" s="19"/>
       <c r="G167" s="7"/>
       <c r="H167" s="7"/>
     </row>
-    <row r="168" spans="1:8" ht="26.25" customHeight="1">
+    <row r="168" spans="1:8" ht="31.5" customHeight="1">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
       <c r="C168" s="8"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
+      <c r="D168" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E168" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F168" s="19"/>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
     </row>
-    <row r="169" spans="1:8" ht="26.25" customHeight="1">
-      <c r="A169" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C169" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D169" s="4"/>
-      <c r="E169" s="16"/>
-      <c r="F169" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="G169" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="H169" s="4"/>
-    </row>
-    <row r="170" spans="1:8" ht="26.25" customHeight="1">
+    <row r="169" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A169" s="7"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F169" s="19"/>
+      <c r="G169" s="7"/>
+      <c r="H169" s="7"/>
+    </row>
+    <row r="170" spans="1:8" ht="31.5" customHeight="1">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="8"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
-      <c r="F170" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="D170" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E170" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F170" s="19"/>
+      <c r="G170" s="7"/>
       <c r="H170" s="7"/>
     </row>
-    <row r="171" spans="1:8" ht="26.25" customHeight="1">
+    <row r="171" spans="1:8" ht="31.5" customHeight="1">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
-      <c r="C171" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7" t="s">
-        <v>209</v>
-      </c>
+      <c r="C171" s="8"/>
+      <c r="D171" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E171" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F171" s="19"/>
+      <c r="G171" s="7"/>
       <c r="H171" s="7"/>
     </row>
-    <row r="172" spans="1:8" ht="26.25" customHeight="1">
+    <row r="172" spans="1:8" ht="31.5" customHeight="1">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
       <c r="C172" s="8"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7" t="s">
-        <v>210</v>
-      </c>
+      <c r="D172" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F172" s="14"/>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
     </row>
-    <row r="173" spans="1:8" ht="39" customHeight="1">
-      <c r="A173" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C173" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D173" s="4"/>
-      <c r="E173" s="4"/>
-      <c r="F173" s="4"/>
-      <c r="G173" s="4"/>
-      <c r="H173" s="4"/>
-    </row>
-    <row r="174" spans="1:8">
+    <row r="173" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A173" s="7"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="8"/>
+      <c r="D173" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E173" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F173" s="14"/>
+      <c r="G173" s="7"/>
+      <c r="H173" s="7"/>
+    </row>
+    <row r="174" spans="1:8" ht="31.5" customHeight="1">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
-      <c r="C174" s="8"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
+      <c r="C174" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F174" s="14"/>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
     </row>
-    <row r="175" spans="1:8" ht="54">
-      <c r="A175" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D175" s="5"/>
-      <c r="E175" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F175" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G175" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H175" s="4"/>
-    </row>
-    <row r="176" spans="1:8" ht="27">
-      <c r="A176" s="8"/>
-      <c r="B176" s="8"/>
-      <c r="C176" s="8"/>
-      <c r="D176" s="7"/>
-      <c r="E176" s="7"/>
-      <c r="F176" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>71</v>
-      </c>
+    <row r="175" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A175" s="7"/>
+      <c r="B175" s="7"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E175" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F175" s="14"/>
+      <c r="G175" s="7"/>
+      <c r="H175" s="7"/>
+    </row>
+    <row r="176" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A176" s="7"/>
+      <c r="B176" s="7"/>
+      <c r="C176" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E176" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="G176" s="7"/>
       <c r="H176" s="7"/>
     </row>
-    <row r="177" spans="1:8" ht="27">
-      <c r="A177" s="8"/>
-      <c r="B177" s="8"/>
+    <row r="177" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A177" s="7"/>
+      <c r="B177" s="7"/>
       <c r="C177" s="8"/>
-      <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>72</v>
-      </c>
+      <c r="D177" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E177" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F177" s="14"/>
+      <c r="G177" s="7"/>
       <c r="H177" s="7"/>
     </row>
-    <row r="178" spans="1:8" ht="27">
-      <c r="A178" s="8"/>
-      <c r="B178" s="8"/>
+    <row r="178" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A178" s="7"/>
+      <c r="B178" s="7"/>
       <c r="C178" s="8"/>
       <c r="D178" s="7"/>
-      <c r="E178" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G178" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="E178" s="15"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
       <c r="H178" s="7"/>
     </row>
-    <row r="179" spans="1:8">
-      <c r="A179" s="8"/>
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
-      <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G179" s="7"/>
-      <c r="H179" s="7"/>
-    </row>
-    <row r="180" spans="1:8" ht="27">
-      <c r="A180" s="8"/>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
-      <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
-      <c r="F180" s="7" t="s">
+    <row r="179" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A179" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" s="16"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="16"/>
+      <c r="F179" s="21"/>
+      <c r="G179" s="16"/>
+      <c r="H179" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A180" s="7"/>
+      <c r="B180" s="7"/>
+      <c r="C180" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="G180" s="7" t="s">
-        <v>55</v>
-      </c>
+      <c r="D180" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="F180" s="7"/>
+      <c r="G180" s="7"/>
       <c r="H180" s="7"/>
     </row>
-    <row r="181" spans="1:8" ht="27">
-      <c r="A181" s="8"/>
-      <c r="B181" s="8"/>
+    <row r="181" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A181" s="7"/>
+      <c r="B181" s="7"/>
       <c r="C181" s="8"/>
-      <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
-      <c r="F181" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="G181" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="D181" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="F181" s="7"/>
+      <c r="G181" s="7"/>
       <c r="H181" s="7"/>
     </row>
-    <row r="182" spans="1:8" ht="40.5">
-      <c r="A182" s="8"/>
-      <c r="B182" s="8"/>
-      <c r="C182" s="8" t="s">
-        <v>50</v>
-      </c>
+    <row r="182" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A182" s="7"/>
+      <c r="B182" s="7"/>
+      <c r="C182" s="8"/>
       <c r="D182" s="7"/>
-      <c r="E182" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F182" s="7" t="s">
-        <v>156</v>
-      </c>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
     </row>
-    <row r="183" spans="1:8" ht="27">
-      <c r="A183" s="8"/>
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
-      <c r="D183" s="7"/>
-      <c r="E183" s="7"/>
-      <c r="F183" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G183" s="7"/>
-      <c r="H183" s="7"/>
-    </row>
-    <row r="184" spans="1:8" ht="27">
-      <c r="A184" s="8"/>
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
-      <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
-      <c r="F184" s="12" t="s">
-        <v>51</v>
-      </c>
+    <row r="183" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A183" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" s="16"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="16"/>
+      <c r="F183" s="21"/>
+      <c r="G183" s="16"/>
+      <c r="H183" s="4"/>
+    </row>
+    <row r="184" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A184" s="7"/>
+      <c r="B184" s="7"/>
+      <c r="C184" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="F184" s="7"/>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
     </row>
-    <row r="185" spans="1:8" ht="40.5">
+    <row r="185" spans="1:8" ht="26.25" customHeight="1">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
-      <c r="C185" s="8" t="s">
-        <v>136</v>
-      </c>
+      <c r="C185" s="8"/>
       <c r="D185" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7" t="s">
-        <v>156</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F185" s="7"/>
       <c r="G185" s="7"/>
       <c r="H185" s="7"/>
     </row>
-    <row r="186" spans="1:8" ht="27">
+    <row r="186" spans="1:8" ht="26.25" customHeight="1">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
-      <c r="C186" s="8"/>
+      <c r="C186" s="7"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
-      <c r="F186" s="7" t="s">
-        <v>81</v>
-      </c>
+      <c r="F186" s="7"/>
       <c r="G186" s="7"/>
       <c r="H186" s="7"/>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" ht="26.25" customHeight="1">
       <c r="A187" s="7"/>
       <c r="B187" s="7"/>
-      <c r="C187" s="8"/>
-      <c r="D187" s="7" t="s">
-        <v>138</v>
-      </c>
+      <c r="C187" s="7"/>
+      <c r="D187" s="7"/>
       <c r="E187" s="7"/>
-      <c r="F187" s="7" t="s">
-        <v>156</v>
-      </c>
+      <c r="F187" s="7"/>
       <c r="G187" s="7"/>
       <c r="H187" s="7"/>
     </row>
-    <row r="188" spans="1:8" ht="27">
+    <row r="188" spans="1:8" ht="26.25" customHeight="1">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
       <c r="C188" s="8"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
-      <c r="F188" s="7" t="s">
-        <v>81</v>
-      </c>
+      <c r="F188" s="7"/>
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
     </row>
-    <row r="189" spans="1:8" ht="40.5">
+    <row r="189" spans="1:8" ht="39" customHeight="1">
       <c r="A189" s="4" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D189" s="5"/>
+        <v>104</v>
+      </c>
+      <c r="C189" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D189" s="4"/>
       <c r="E189" s="4"/>
-      <c r="F189" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G189" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
       <c r="H189" s="4"/>
     </row>
-    <row r="190" spans="1:8" ht="27">
+    <row r="190" spans="1:8">
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
       <c r="C190" s="8"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
-      <c r="F190" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="F190" s="7"/>
       <c r="G190" s="7"/>
       <c r="H190" s="7"/>
     </row>
-    <row r="191" spans="1:8" ht="27">
-      <c r="A191" s="7"/>
-      <c r="B191" s="7"/>
-      <c r="C191" s="8"/>
-      <c r="D191" s="7"/>
-      <c r="E191" s="7"/>
-      <c r="F191" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G191" s="7"/>
-      <c r="H191" s="7"/>
-    </row>
-    <row r="192" spans="1:8" ht="27">
-      <c r="A192" s="7"/>
-      <c r="B192" s="7"/>
-      <c r="C192" s="8" t="s">
-        <v>184</v>
-      </c>
+    <row r="191" spans="1:8" ht="54">
+      <c r="A191" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C191" s="5"/>
+      <c r="D191" s="5"/>
+      <c r="E191" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G191" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="H191" s="4"/>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="8"/>
+      <c r="B192" s="8"/>
+      <c r="C192" s="8"/>
       <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
+      <c r="E192" s="7" t="s">
+        <v>214</v>
+      </c>
       <c r="F192" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G192" s="7"/>
+        <v>68</v>
+      </c>
+      <c r="G192" s="7" t="s">
+        <v>213</v>
+      </c>
       <c r="H192" s="7"/>
     </row>
-    <row r="193" spans="1:8" ht="40.5">
-      <c r="A193" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D193" s="5"/>
-      <c r="E193" s="4"/>
-      <c r="F193" s="4"/>
-      <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
-    </row>
-    <row r="194" spans="1:8">
-      <c r="C194" s="8"/>
+    <row r="193" spans="1:8" ht="27">
+      <c r="A193" s="8"/>
+      <c r="B193" s="8"/>
+      <c r="C193" s="8"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F193" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G193" s="7"/>
+      <c r="H193" s="7"/>
+    </row>
+    <row r="194" spans="1:8" ht="40.5">
+      <c r="A194" s="8"/>
+      <c r="B194" s="8"/>
+      <c r="C194" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
+      <c r="E194" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>212</v>
+      </c>
       <c r="G194" s="7"/>
       <c r="H194" s="7"/>
     </row>
     <row r="195" spans="1:8" ht="40.5">
-      <c r="A195" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B195" s="4" t="s">
+      <c r="A195" s="7"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F195" s="7"/>
+      <c r="G195" s="7"/>
+      <c r="H195" s="7"/>
+    </row>
+    <row r="196" spans="1:8" ht="40.5">
+      <c r="A196" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B196" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C195" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D195" s="4"/>
-      <c r="E195" s="4"/>
-      <c r="F195" s="4"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
-    </row>
-    <row r="196" spans="1:8">
-      <c r="A196" s="8"/>
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
-      <c r="G196" s="7"/>
-      <c r="H196" s="7"/>
-    </row>
-    <row r="197" spans="1:8">
-      <c r="A197" s="8"/>
-      <c r="B197" s="8"/>
+      <c r="C196" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D196" s="5"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H196" s="4"/>
+    </row>
+    <row r="197" spans="1:8" ht="27">
+      <c r="A197" s="7"/>
+      <c r="B197" s="7"/>
       <c r="C197" s="8"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7"/>
-      <c r="F197" s="7"/>
+      <c r="F197" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="G197" s="7"/>
       <c r="H197" s="7"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="D198" s="9"/>
-      <c r="E198" s="9"/>
-      <c r="F198" s="9"/>
-      <c r="G198" s="9"/>
+      <c r="A198" s="7"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="8"/>
+      <c r="D198" s="7"/>
+      <c r="E198" s="7"/>
+      <c r="F198" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G198" s="7"/>
+      <c r="H198" s="7"/>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" s="7"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D199" s="7"/>
+      <c r="E199" s="7"/>
+      <c r="F199" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G199" s="7"/>
+      <c r="H199" s="7"/>
+    </row>
+    <row r="200" spans="1:8" ht="40.5">
+      <c r="A200" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D200" s="5"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4"/>
+      <c r="G200" s="4"/>
+      <c r="H200" s="4"/>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="C201" s="8"/>
+      <c r="D201" s="7"/>
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
+      <c r="G201" s="7"/>
+      <c r="H201" s="7"/>
+    </row>
+    <row r="202" spans="1:8" ht="40.5">
+      <c r="A202" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D202" s="4"/>
+      <c r="E202" s="4"/>
+      <c r="F202" s="4"/>
+      <c r="G202" s="4"/>
+      <c r="H202" s="4"/>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="8"/>
+      <c r="B203" s="8"/>
+      <c r="C203" s="8"/>
+      <c r="D203" s="7"/>
+      <c r="E203" s="7"/>
+      <c r="F203" s="7"/>
+      <c r="G203" s="7"/>
+      <c r="H203" s="7"/>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" s="8"/>
+      <c r="B204" s="8"/>
+      <c r="C204" s="8"/>
+      <c r="D204" s="7"/>
+      <c r="E204" s="7"/>
+      <c r="F204" s="7"/>
+      <c r="G204" s="7"/>
+      <c r="H204" s="7"/>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
+      <c r="F205" s="9"/>
+      <c r="G205" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H100">
